--- a/Certificados legales.xlsx
+++ b/Certificados legales.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://globalkomatsu-my.sharepoint.com/personal/cristopher_bravo_global_komatsu/Documents/Escritorio/Control Acreditaciones Komatsu RT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{D3CB6B16-8A20-4C23-86D3-67B5B311B6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DB3867A-0C25-45F0-843E-DC4916C041CC}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{D3CB6B16-8A20-4C23-86D3-67B5B311B6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C262E834-6BC7-4233-869B-5D0382B036AC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{74EC7066-F67C-4C10-83B2-DD23CDD4CD17}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{74EC7066-F67C-4C10-83B2-DD23CDD4CD17}"/>
   </bookViews>
   <sheets>
     <sheet name="ALTURA" sheetId="2" r:id="rId1"/>
     <sheet name="RIGGER B" sheetId="4" r:id="rId2"/>
     <sheet name="TRABAJO EN CALIENTE" sheetId="3" r:id="rId3"/>
-    <sheet name="Hoja1" sheetId="1" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ALTURA!$A$1:$E$306</definedName>
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="616">
   <si>
     <t>ZAKK ELIZALDE DIAZ</t>
   </si>
@@ -1895,12 +1894,6 @@
   </si>
   <si>
     <t xml:space="preserve">RUT </t>
-  </si>
-  <si>
-    <t>NO APLICA</t>
-  </si>
-  <si>
-    <t>RIGGER B</t>
   </si>
   <si>
     <t>RUT (CFK)</t>
@@ -1910,9 +1903,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2038,7 +2028,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2092,12 +2082,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2264,9 +2248,6 @@
           <cell r="AQ4" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS4" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT4" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -2445,9 +2426,6 @@
           <cell r="AQ12" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS12" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT12" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -2551,9 +2529,6 @@
           <cell r="AQ17" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS17" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT17" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -2750,9 +2725,6 @@
           <cell r="AQ25" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS25" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT25" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -2770,9 +2742,6 @@
           <cell r="AQ26" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS26" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT26" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -2905,9 +2874,6 @@
           <cell r="AQ32" t="str">
             <v>PENDIENTE</v>
           </cell>
-          <cell r="AS32" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT32" t="str">
             <v>TOMADO</v>
           </cell>
@@ -2928,9 +2894,6 @@
           <cell r="AQ33" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS33" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT33" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -3043,9 +3006,6 @@
           <cell r="AQ38" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS38" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT38" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -3086,9 +3046,6 @@
           <cell r="AQ40" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS40" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT40" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -3106,9 +3063,6 @@
           <cell r="AQ41" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS41" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT41" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -3272,9 +3226,6 @@
           <cell r="AQ49" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS49" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT49" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -3528,9 +3479,6 @@
           <cell r="E60" t="str">
             <v>17.289.071-7</v>
           </cell>
-          <cell r="AS60" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT60" t="str">
             <v>GESTIONAR</v>
           </cell>
@@ -3669,9 +3617,6 @@
           <cell r="AQ66" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS66" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT66" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -4008,9 +3953,6 @@
           <cell r="AQ81" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS81" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT81" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -4051,9 +3993,6 @@
           <cell r="AQ83" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS83" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT83" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -4143,9 +4082,6 @@
           <cell r="AQ87" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS87" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT87" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -4266,9 +4202,6 @@
           <cell r="AQ93" t="str">
             <v>CALXXX</v>
           </cell>
-          <cell r="AS93" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT93" t="str">
             <v>VENCIDO</v>
           </cell>
@@ -4491,9 +4424,6 @@
           <cell r="AQ102" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS102" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT102" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -4548,9 +4478,6 @@
           <cell r="E105" t="str">
             <v>15.615.715-5</v>
           </cell>
-          <cell r="AS105" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT105" t="e">
             <v>#REF!</v>
           </cell>
@@ -4844,9 +4771,6 @@
           <cell r="AQ118" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS118" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT118" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -4933,9 +4857,6 @@
           <cell r="AQ122" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS122" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT122" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -4953,9 +4874,6 @@
           <cell r="AQ123" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS123" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT123" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -5028,9 +4946,6 @@
           <cell r="AQ126" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS126" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT126" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -5369,9 +5284,6 @@
           <cell r="AQ142" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS142" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT142" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -5822,9 +5734,6 @@
           <cell r="E163" t="str">
             <v>16.453.544-4</v>
           </cell>
-          <cell r="AS163" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT163" t="e">
             <v>#REF!</v>
           </cell>
@@ -5845,9 +5754,6 @@
           <cell r="AQ164" t="str">
             <v>CAL238098</v>
           </cell>
-          <cell r="AS164" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT164" t="str">
             <v>TOMADO</v>
           </cell>
@@ -6009,9 +5915,6 @@
           <cell r="AQ171" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS171" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT171" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -6161,9 +6064,6 @@
           <cell r="AQ178" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS178" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT178" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -6362,9 +6262,6 @@
           <cell r="AQ187" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS187" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT187" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -6382,9 +6279,6 @@
           <cell r="AQ188" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS188" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT188" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -6712,9 +6606,6 @@
           <cell r="AQ203" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS203" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT203" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -6798,9 +6689,6 @@
           <cell r="AQ207" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS207" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT207" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7129,9 +7017,6 @@
           <cell r="AQ221" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS221" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT221" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7169,9 +7054,6 @@
           <cell r="AQ223" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS223" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT223" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7215,9 +7097,6 @@
           <cell r="AQ225" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS225" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT225" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7235,9 +7114,6 @@
           <cell r="AQ226" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS226" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT226" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7252,9 +7128,6 @@
           <cell r="E227" t="str">
             <v>20.167.551-0</v>
           </cell>
-          <cell r="AS227" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT227" t="e">
             <v>#REF!</v>
           </cell>
@@ -7332,9 +7205,6 @@
           <cell r="AQ231" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS231" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT231" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7481,9 +7351,6 @@
           <cell r="AQ238" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS238" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT238" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7518,9 +7385,6 @@
           <cell r="E240" t="str">
             <v>14.413.359-5</v>
           </cell>
-          <cell r="AS240" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT240" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7653,9 +7517,6 @@
           <cell r="AQ246" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS246" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT246" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7894,9 +7755,6 @@
           <cell r="AQ257" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS257" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT257" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -7917,9 +7775,6 @@
           <cell r="AQ258" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS258" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT258" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8023,9 +7878,6 @@
           <cell r="AQ263" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS263" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT263" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8092,9 +7944,6 @@
           <cell r="AQ266" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS266" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT266" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8175,9 +8024,6 @@
           <cell r="AQ270" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS270" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT270" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8261,9 +8107,6 @@
           <cell r="AQ274" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS274" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT274" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8321,9 +8164,6 @@
           <cell r="AQ277" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS277" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT277" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8430,9 +8270,6 @@
           <cell r="AQ282" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS282" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT282" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8519,9 +8356,6 @@
           <cell r="AQ286" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS286" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT286" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8539,9 +8373,6 @@
           <cell r="AQ287" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS287" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT287" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8605,9 +8436,6 @@
           <cell r="AQ290" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS290" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT290" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8645,9 +8473,6 @@
           <cell r="E292" t="str">
             <v>15.924.486-5</v>
           </cell>
-          <cell r="AS292" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT292" t="str">
             <v>GESTIONAR</v>
           </cell>
@@ -8731,9 +8556,6 @@
           <cell r="AQ296" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS296" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT296" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8751,9 +8573,6 @@
           <cell r="AQ297" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS297" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT297" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8900,9 +8719,6 @@
           <cell r="AQ304" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS304" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT304" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -8969,9 +8785,6 @@
           <cell r="AQ307" t="str">
             <v>CAL238098</v>
           </cell>
-          <cell r="AS307" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT307" t="str">
             <v>TOMADO</v>
           </cell>
@@ -8992,9 +8805,6 @@
           <cell r="AQ308" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS308" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT308" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -9029,9 +8839,6 @@
           <cell r="AQ310" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS310" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT310" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -9049,9 +8856,6 @@
           <cell r="AQ311" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS311" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT311" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -9290,9 +9094,6 @@
           <cell r="AQ322" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS322" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT322" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -9330,9 +9131,6 @@
           <cell r="AQ324" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS324" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT324" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -9350,9 +9148,6 @@
           <cell r="AQ325" t="str">
             <v>NO APLICA</v>
           </cell>
-          <cell r="AS325" t="str">
-            <v>NO APLICA</v>
-          </cell>
           <cell r="AT325" t="str">
             <v>NO APLICA</v>
           </cell>
@@ -9368,9 +9163,6 @@
             <v>19.824.546-1</v>
           </cell>
           <cell r="AQ326" t="str">
-            <v>NO APLICA</v>
-          </cell>
-          <cell r="AS326" t="str">
             <v>NO APLICA</v>
           </cell>
           <cell r="AT326" t="str">
@@ -9863,9 +9655,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D4" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D4" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E4" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10003,9 +9795,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D11" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D11" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E11" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10103,9 +9895,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D16" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D16" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E16" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10243,9 +10035,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D23" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D23" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10263,9 +10055,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D24" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D24" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E24" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10363,9 +10155,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>PENDIENTE</v>
       </c>
-      <c r="D29" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D29" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10383,9 +10175,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D30" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D30" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E30" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10483,9 +10275,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D35" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D35" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E35" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10523,9 +10315,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D37" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D37" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E37" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10543,9 +10335,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D38" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D38" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E38" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10703,9 +10495,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D46" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D46" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E46" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -10903,9 +10695,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D56" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E56" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -11023,9 +10815,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D62" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D62" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E62" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -11084,7 +10876,8 @@
         <v>CAL238098</v>
       </c>
       <c r="D65" s="2">
-        <v>46224</v>
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>45980</v>
       </c>
       <c r="E65" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -11302,9 +11095,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D76" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D76" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E76" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -11342,9 +11135,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D78" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D78" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E78" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -11422,9 +11215,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D82" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D82" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E82" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -11522,9 +11315,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>CALXXX</v>
       </c>
-      <c r="D87" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D87" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E87" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -11702,9 +11495,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D96" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D96" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E96" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -11762,9 +11555,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>0</v>
       </c>
-      <c r="D99" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D99" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E99" s="1" t="e">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -12022,9 +11815,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D112" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D112" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E112" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -12102,9 +11895,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D116" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D116" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E116" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -12122,9 +11915,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D117" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D117" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E117" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -12182,9 +11975,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D120" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D120" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E120" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -12502,9 +12295,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D136" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D136" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E136" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -12862,9 +12655,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>0</v>
       </c>
-      <c r="D154" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D154" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E154" s="1" t="e">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -12882,9 +12675,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>CAL238098</v>
       </c>
-      <c r="D155" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D155" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E155" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -13022,9 +12815,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D162" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D162" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E162" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -13142,9 +12935,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D168" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D168" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E168" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -13322,9 +13115,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D177" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D177" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E177" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -13342,9 +13135,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D178" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D178" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E178" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -13622,9 +13415,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D192" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D192" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E192" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -13702,9 +13495,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D196" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D196" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E196" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -13962,9 +13755,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D209" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D209" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E209" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14002,9 +13795,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D211" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D211" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E211" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14042,9 +13835,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D213" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D213" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E213" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14062,9 +13855,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D214" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D214" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E214" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14082,9 +13875,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>0</v>
       </c>
-      <c r="D215" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D215" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E215" s="1" t="e">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14142,9 +13935,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D218" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D218" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E218" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14262,9 +14055,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D224" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D224" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E224" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14302,9 +14095,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>0</v>
       </c>
-      <c r="D226" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D226" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E226" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14382,9 +14175,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D230" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D230" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E230" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14582,9 +14375,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D240" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D240" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E240" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14602,9 +14395,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D241" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D241" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E241" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14682,9 +14475,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D245" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D245" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E245" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14742,9 +14535,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D248" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D248" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E248" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14802,9 +14595,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D251" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D251" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E251" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14882,9 +14675,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D255" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D255" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E255" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -14942,9 +14735,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D258" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D258" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E258" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15022,9 +14815,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D262" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D262" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E262" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15102,9 +14895,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D266" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D266" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E266" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15122,9 +14915,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D267" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D267" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E267" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15182,9 +14975,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D270" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D270" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E270" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15302,9 +15095,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D276" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D276" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E276" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15322,9 +15115,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D277" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D277" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E277" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15522,9 +15315,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>CAL238098</v>
       </c>
-      <c r="D287" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D287" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E287" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15542,9 +15335,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D288" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D288" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E288" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15562,9 +15355,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D289" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D289" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E289" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15582,9 +15375,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D290" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D290" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E290" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15762,9 +15555,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D299" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D299" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E299" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15802,9 +15595,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D301" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D301" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E301" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15822,9 +15615,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D302" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D302" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E302" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15842,9 +15635,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AQ:$AQ)</f>
         <v>NO APLICA</v>
       </c>
-      <c r="D303" s="2" t="str">
-        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
-        <v>NO APLICA</v>
+      <c r="D303" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AS:$AS)</f>
+        <v>0</v>
       </c>
       <c r="E303" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$AT:$AT)</f>
@@ -15938,7 +15731,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>613</v>
@@ -15950,7 +15743,7 @@
         <v>611</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -16344,7 +16137,10 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL233182</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
+      </c>
       <c r="E21" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
         <v>REPROBADO</v>
@@ -16361,8 +16157,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>615</v>
+      <c r="D22" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E22" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16380,8 +16177,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>615</v>
+      <c r="D23" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16399,8 +16197,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>615</v>
+      <c r="D24" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E24" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16418,8 +16217,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>615</v>
+      <c r="D25" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E25" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16437,8 +16237,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>615</v>
+      <c r="D26" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E26" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16456,8 +16257,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>615</v>
+      <c r="D27" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E27" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16475,8 +16277,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>615</v>
+      <c r="D28" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16494,8 +16297,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>615</v>
+      <c r="D29" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16514,6 +16318,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D30" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E30" s="1" t="str">
@@ -16533,6 +16338,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D31" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E31" s="1" t="str">
@@ -16552,6 +16358,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D32" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E32" s="1" t="str">
@@ -16570,8 +16377,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>615</v>
+      <c r="D33" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E33" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16589,8 +16397,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>615</v>
+      <c r="D34" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E34" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16608,8 +16417,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>615</v>
+      <c r="D35" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E35" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16627,7 +16437,10 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL233182</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
+      </c>
       <c r="E36" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
         <v>REPROBADO</v>
@@ -16644,8 +16457,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>615</v>
+      <c r="D37" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E37" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16664,6 +16478,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D38" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E38" s="1" t="str">
@@ -16682,8 +16497,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>615</v>
+      <c r="D39" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E39" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16701,8 +16517,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>615</v>
+      <c r="D40" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E40" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16720,8 +16537,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>615</v>
+      <c r="D41" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E41" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16739,8 +16557,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>615</v>
+      <c r="D42" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E42" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16759,6 +16578,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D43" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E43" s="1" t="str">
@@ -16778,6 +16598,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D44" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E44" s="1" t="str">
@@ -16796,8 +16617,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>615</v>
+      <c r="D45" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E45" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16815,8 +16637,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>615</v>
+      <c r="D46" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E46" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16835,6 +16658,7 @@
         <v>CAL231172</v>
       </c>
       <c r="D47" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46673</v>
       </c>
       <c r="E47" s="1" t="str">
@@ -16854,6 +16678,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D48" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E48" s="1" t="str">
@@ -16872,8 +16697,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>615</v>
+      <c r="D49" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E49" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16892,6 +16718,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D50" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E50" s="1" t="str">
@@ -16911,6 +16738,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D51" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E51" s="1" t="str">
@@ -16929,8 +16757,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>615</v>
+      <c r="D52" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E52" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16948,8 +16777,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>615</v>
+      <c r="D53" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E53" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16967,8 +16797,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>615</v>
+      <c r="D54" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E54" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -16986,8 +16817,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>615</v>
+      <c r="D55" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E55" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17006,6 +16838,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D56" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E56" s="1" t="str">
@@ -17024,8 +16857,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>615</v>
+      <c r="D57" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E57" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17044,6 +16878,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D58" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E58" s="1" t="str">
@@ -17063,6 +16898,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D59" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46031</v>
       </c>
       <c r="E59" s="1" t="str">
@@ -17082,6 +16918,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D60" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E60" s="1" t="str">
@@ -17101,6 +16938,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D61" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E61" s="1" t="str">
@@ -17119,8 +16957,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>615</v>
+      <c r="D62" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E62" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17138,8 +16977,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>615</v>
+      <c r="D63" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E63" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17158,6 +16998,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D64" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E64" s="1" t="str">
@@ -17176,8 +17017,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>615</v>
+      <c r="D65" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E65" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17196,6 +17038,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D66" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E66" s="1" t="str">
@@ -17214,8 +17057,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>615</v>
+      <c r="D67" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E67" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17233,8 +17077,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>615</v>
+      <c r="D68" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E68" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17253,6 +17098,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D69" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E69" s="1" t="str">
@@ -17271,8 +17117,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>615</v>
+      <c r="D70" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E70" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17290,8 +17137,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>615</v>
+      <c r="D71" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E71" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17309,8 +17157,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>615</v>
+      <c r="D72" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E72" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17328,8 +17177,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>615</v>
+      <c r="D73" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E73" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17347,8 +17197,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>615</v>
+      <c r="D74" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E74" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17366,8 +17217,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>615</v>
+      <c r="D75" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E75" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17386,6 +17238,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D76" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E76" s="1" t="str">
@@ -17404,8 +17257,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>615</v>
+      <c r="D77" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E77" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17424,6 +17278,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D78" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E78" s="1" t="str">
@@ -17442,8 +17297,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>615</v>
+      <c r="D79" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E79" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17462,6 +17318,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D80" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E80" s="1" t="str">
@@ -17480,8 +17337,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>615</v>
+      <c r="D81" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E81" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17499,8 +17357,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>615</v>
+      <c r="D82" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E82" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17519,6 +17378,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D83" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E83" s="1" t="str">
@@ -17537,8 +17397,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>615</v>
+      <c r="D84" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E84" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17556,8 +17417,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>615</v>
+      <c r="D85" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E85" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17575,8 +17437,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>615</v>
+      <c r="D86" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E86" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17594,8 +17457,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>615</v>
+      <c r="D87" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E87" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17613,8 +17477,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>615</v>
+      <c r="D88" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E88" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17633,6 +17498,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D89" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E89" s="1" t="str">
@@ -17651,8 +17517,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>615</v>
+      <c r="D90" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E90" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17670,8 +17537,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>615</v>
+      <c r="D91" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E91" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17690,6 +17558,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D92" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E92" s="1" t="str">
@@ -17709,6 +17578,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D93" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E93" s="1" t="str">
@@ -17728,6 +17598,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D94" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E94" s="1" t="str">
@@ -17746,8 +17617,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>615</v>
+      <c r="D95" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E95" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17765,8 +17637,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>615</v>
+      <c r="D96" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E96" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17785,6 +17658,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D97" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E97" s="1" t="str">
@@ -17803,8 +17677,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>615</v>
+      <c r="D98" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E98" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17822,8 +17697,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>615</v>
+      <c r="D99" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E99" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17842,6 +17718,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D100" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E100" s="1" t="str">
@@ -17860,8 +17737,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>615</v>
+      <c r="D101" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E101" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17880,6 +17758,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D102" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E102" s="1" t="str">
@@ -17899,6 +17778,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D103" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E103" s="1" t="str">
@@ -17918,6 +17798,7 @@
         <v>CAL231172</v>
       </c>
       <c r="D104" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46673</v>
       </c>
       <c r="E104" s="1" t="str">
@@ -17936,8 +17817,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>615</v>
+      <c r="D105" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E105" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17955,8 +17837,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>615</v>
+      <c r="D106" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E106" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -17975,6 +17858,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D107" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E107" s="1" t="str">
@@ -17993,8 +17877,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>615</v>
+      <c r="D108" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E108" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18012,8 +17897,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>615</v>
+      <c r="D109" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E109" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18031,8 +17917,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>615</v>
+      <c r="D110" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E110" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18050,8 +17937,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>615</v>
+      <c r="D111" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E111" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18070,6 +17958,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D112" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E112" s="1" t="str">
@@ -18088,8 +17977,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>615</v>
+      <c r="D113" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E113" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18107,8 +17997,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>615</v>
+      <c r="D114" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E114" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18127,6 +18018,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D115" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E115" s="1" t="str">
@@ -18146,6 +18038,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D116" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E116" s="1" t="str">
@@ -18164,8 +18057,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>615</v>
+      <c r="D117" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E117" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18184,6 +18078,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D118" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E118" s="1" t="str">
@@ -18202,8 +18097,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>615</v>
+      <c r="D119" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E119" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18221,8 +18117,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>615</v>
+      <c r="D120" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E120" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18240,8 +18137,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>615</v>
+      <c r="D121" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E121" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18260,6 +18158,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D122" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E122" s="1" t="str">
@@ -18279,6 +18178,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D123" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E123" s="1" t="str">
@@ -18298,6 +18198,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D124" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E124" s="1" t="str">
@@ -18317,6 +18218,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D125" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E125" s="1" t="str">
@@ -18336,6 +18238,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D126" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E126" s="1" t="str">
@@ -18354,8 +18257,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>615</v>
+      <c r="D127" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E127" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18374,6 +18278,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D128" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E128" s="1" t="str">
@@ -18393,6 +18298,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D129" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E129" s="1" t="str">
@@ -18411,8 +18317,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D130" s="2" t="s">
-        <v>615</v>
+      <c r="D130" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E130" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18431,6 +18338,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D131" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E131" s="1" t="str">
@@ -18449,8 +18357,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>615</v>
+      <c r="D132" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E132" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18469,6 +18378,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D133" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E133" s="1" t="str">
@@ -18487,8 +18397,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D134" s="2" t="s">
-        <v>615</v>
+      <c r="D134" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E134" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18506,8 +18417,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>615</v>
+      <c r="D135" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E135" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18525,8 +18437,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>615</v>
+      <c r="D136" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E136" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18544,8 +18457,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D137" s="2" t="s">
-        <v>615</v>
+      <c r="D137" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E137" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18564,6 +18478,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D138" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E138" s="1" t="str">
@@ -18582,8 +18497,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>615</v>
+      <c r="D139" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E139" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18601,8 +18517,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>615</v>
+      <c r="D140" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E140" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18621,6 +18538,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D141" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E141" s="1" t="str">
@@ -18640,6 +18558,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D142" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E142" s="1" t="str">
@@ -18659,6 +18578,7 @@
         <v>CAL231172</v>
       </c>
       <c r="D143" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46673</v>
       </c>
       <c r="E143" s="1" t="str">
@@ -18677,8 +18597,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D144" s="2" t="s">
-        <v>615</v>
+      <c r="D144" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E144" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18696,8 +18617,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D145" s="2" t="s">
-        <v>615</v>
+      <c r="D145" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E145" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18715,8 +18637,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D146" s="2" t="s">
-        <v>615</v>
+      <c r="D146" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E146" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18734,8 +18657,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D147" s="2" t="s">
-        <v>615</v>
+      <c r="D147" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E147" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18754,6 +18678,7 @@
         <v>CAL231172</v>
       </c>
       <c r="D148" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46673</v>
       </c>
       <c r="E148" s="1" t="str">
@@ -18773,6 +18698,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D149" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E149" s="1" t="str">
@@ -18792,6 +18718,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D150" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E150" s="1" t="str">
@@ -18811,6 +18738,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D151" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E151" s="1" t="str">
@@ -18829,8 +18757,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D152" s="2" t="s">
-        <v>615</v>
+      <c r="D152" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E152" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18849,6 +18778,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D153" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E153" s="1" t="str">
@@ -18868,6 +18798,7 @@
         <v>CAL231172</v>
       </c>
       <c r="D154" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46673</v>
       </c>
       <c r="E154" s="1" t="str">
@@ -18886,8 +18817,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>615</v>
+      <c r="D155" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E155" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18906,6 +18838,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D156" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E156" s="1" t="str">
@@ -18925,6 +18858,7 @@
         <v>CAL231172</v>
       </c>
       <c r="D157" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46673</v>
       </c>
       <c r="E157" s="1" t="str">
@@ -18944,6 +18878,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D158" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E158" s="1" t="str">
@@ -18962,8 +18897,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>615</v>
+      <c r="D159" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E159" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -18982,6 +18918,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D160" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E160" s="1" t="str">
@@ -19000,8 +18937,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>615</v>
+      <c r="D161" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E161" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19020,6 +18958,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D162" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E162" s="1" t="str">
@@ -19038,8 +18977,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>615</v>
+      <c r="D163" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E163" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19057,8 +18997,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D164" s="2" t="s">
-        <v>615</v>
+      <c r="D164" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E164" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19076,8 +19017,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D165" s="2" t="s">
-        <v>615</v>
+      <c r="D165" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>45900</v>
       </c>
       <c r="E165" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19096,6 +19038,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D166" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E166" s="1" t="str">
@@ -19114,8 +19057,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D167" s="2" t="s">
-        <v>615</v>
+      <c r="D167" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E167" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19133,8 +19077,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D168" s="2" t="s">
-        <v>615</v>
+      <c r="D168" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E168" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19152,8 +19097,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D169" s="2" t="s">
-        <v>615</v>
+      <c r="D169" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E169" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19171,8 +19117,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D170" s="2" t="s">
-        <v>615</v>
+      <c r="D170" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E170" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19190,8 +19137,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D171" s="2" t="s">
-        <v>615</v>
+      <c r="D171" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E171" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19209,8 +19157,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D172" s="2" t="s">
-        <v>615</v>
+      <c r="D172" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E172" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19228,8 +19177,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D173" s="2" t="s">
-        <v>615</v>
+      <c r="D173" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E173" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19247,8 +19197,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D174" s="2" t="s">
-        <v>615</v>
+      <c r="D174" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E174" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19266,8 +19217,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D175" s="2" t="s">
-        <v>615</v>
+      <c r="D175" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E175" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19285,8 +19237,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D176" s="2" t="s">
-        <v>615</v>
+      <c r="D176" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E176" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19304,8 +19257,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D177" s="2" t="s">
-        <v>615</v>
+      <c r="D177" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E177" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19323,8 +19277,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D178" s="2" t="s">
-        <v>615</v>
+      <c r="D178" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>46031</v>
       </c>
       <c r="E178" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19343,6 +19298,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D179" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E179" s="1" t="str">
@@ -19361,8 +19317,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D180" s="2" t="s">
-        <v>615</v>
+      <c r="D180" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E180" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19381,6 +19338,7 @@
         <v>CAL227483-3</v>
       </c>
       <c r="D181" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46589</v>
       </c>
       <c r="E181" s="1" t="str">
@@ -19399,8 +19357,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D182" s="2" t="s">
-        <v>615</v>
+      <c r="D182" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E182" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19418,8 +19377,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D183" s="2" t="s">
-        <v>615</v>
+      <c r="D183" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E183" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19437,8 +19397,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D184" s="2" t="s">
-        <v>615</v>
+      <c r="D184" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E184" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19456,8 +19417,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D185" s="2" t="s">
-        <v>615</v>
+      <c r="D185" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E185" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19475,8 +19437,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D186" s="2" t="s">
-        <v>615</v>
+      <c r="D186" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E186" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19494,8 +19457,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D187" s="2" t="s">
-        <v>615</v>
+      <c r="D187" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E187" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19513,8 +19477,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D188" s="2" t="s">
-        <v>615</v>
+      <c r="D188" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E188" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19532,8 +19497,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D189" s="2" t="s">
-        <v>615</v>
+      <c r="D189" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E189" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19551,8 +19517,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D190" s="2" t="s">
-        <v>615</v>
+      <c r="D190" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E190" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19570,8 +19537,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D191" s="2" t="s">
-        <v>615</v>
+      <c r="D191" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E191" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19589,8 +19557,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D192" s="2" t="s">
-        <v>615</v>
+      <c r="D192" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E192" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19608,8 +19577,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D193" s="2" t="s">
-        <v>615</v>
+      <c r="D193" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E193" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19627,8 +19597,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D194" s="2" t="s">
-        <v>615</v>
+      <c r="D194" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E194" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19646,8 +19617,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D195" s="2" t="s">
-        <v>615</v>
+      <c r="D195" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E195" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19666,6 +19638,7 @@
         <v>CAL220586</v>
       </c>
       <c r="D196" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E196" s="1" t="str">
@@ -19684,8 +19657,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D197" s="2" t="s">
-        <v>615</v>
+      <c r="D197" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E197" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19703,8 +19677,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D198" s="2" t="s">
-        <v>615</v>
+      <c r="D198" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E198" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19722,8 +19697,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D199" s="2" t="s">
-        <v>615</v>
+      <c r="D199" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E199" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19741,8 +19717,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D200" s="2" t="s">
-        <v>615</v>
+      <c r="D200" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E200" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19760,8 +19737,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D201" s="2" t="s">
-        <v>615</v>
+      <c r="D201" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E201" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19779,8 +19757,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D202" s="2" t="s">
-        <v>615</v>
+      <c r="D202" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E202" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19798,8 +19777,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D203" s="2" t="s">
-        <v>615</v>
+      <c r="D203" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E203" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19817,8 +19797,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D204" s="2" t="s">
-        <v>615</v>
+      <c r="D204" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E204" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19836,8 +19817,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D205" s="2" t="s">
-        <v>615</v>
+      <c r="D205" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E205" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19855,8 +19837,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D206" s="2" t="s">
-        <v>615</v>
+      <c r="D206" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E206" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19874,8 +19857,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D207" s="2" t="s">
-        <v>615</v>
+      <c r="D207" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E207" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19893,8 +19877,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D208" s="2" t="s">
-        <v>615</v>
+      <c r="D208" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E208" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19912,8 +19897,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D209" s="2" t="s">
-        <v>615</v>
+      <c r="D209" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E209" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19931,8 +19917,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D210" s="2" t="s">
-        <v>615</v>
+      <c r="D210" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E210" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19950,8 +19937,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D211" s="2" t="s">
-        <v>615</v>
+      <c r="D211" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E211" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -19970,6 +19958,7 @@
         <v>CAL227381</v>
       </c>
       <c r="D212" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E212" s="1" t="str">
@@ -19988,8 +19977,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D213" s="2" t="s">
-        <v>615</v>
+      <c r="D213" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E213" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20007,8 +19997,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D214" s="2" t="s">
-        <v>615</v>
+      <c r="D214" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E214" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20026,8 +20017,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D215" s="2" t="s">
-        <v>615</v>
+      <c r="D215" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E215" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20045,8 +20037,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D216" s="2" t="s">
-        <v>615</v>
+      <c r="D216" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>46031</v>
       </c>
       <c r="E216" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20064,8 +20057,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D217" s="2" t="s">
-        <v>615</v>
+      <c r="D217" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E217" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20083,8 +20077,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D218" s="2" t="s">
-        <v>615</v>
+      <c r="D218" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E218" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20102,8 +20097,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D219" s="2" t="s">
-        <v>615</v>
+      <c r="D219" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E219" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20121,8 +20117,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D220" s="2" t="s">
-        <v>615</v>
+      <c r="D220" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E220" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20140,7 +20137,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL233182</v>
       </c>
-      <c r="D221" s="22">
+      <c r="D221" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E221" s="1" t="str">
@@ -20159,8 +20157,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>615</v>
+      <c r="D222" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E222" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20178,8 +20177,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D223" s="2" t="s">
-        <v>615</v>
+      <c r="D223" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E223" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20197,8 +20197,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D224" s="2" t="s">
-        <v>615</v>
+      <c r="D224" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E224" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20216,8 +20217,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D225" s="2" t="s">
-        <v>615</v>
+      <c r="D225" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E225" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20235,8 +20237,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D226" s="2" t="s">
-        <v>615</v>
+      <c r="D226" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E226" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20254,8 +20257,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D227" s="2" t="s">
-        <v>615</v>
+      <c r="D227" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E227" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20273,7 +20277,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL227381</v>
       </c>
-      <c r="D228" s="22">
+      <c r="D228" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E228" s="1" t="str">
@@ -20292,8 +20297,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D229" s="2" t="s">
-        <v>615</v>
+      <c r="D229" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E229" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20311,8 +20317,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>615</v>
+      <c r="D230" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E230" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20330,8 +20337,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D231" s="2" t="s">
-        <v>615</v>
+      <c r="D231" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E231" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20349,8 +20357,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>615</v>
+      <c r="D232" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E232" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20368,8 +20377,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>615</v>
+      <c r="D233" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E233" s="1" t="str">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20387,8 +20397,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D234" s="2" t="s">
-        <v>615</v>
+      <c r="D234" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E234" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20406,7 +20417,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL231172</v>
       </c>
-      <c r="D235" s="22">
+      <c r="D235" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46673</v>
       </c>
       <c r="E235" s="1" t="str">
@@ -20425,7 +20437,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL227381</v>
       </c>
-      <c r="D236" s="22">
+      <c r="D236" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E236" s="1" t="str">
@@ -20444,8 +20457,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>615</v>
+      <c r="D237" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E237" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20464,6 +20478,7 @@
         <v>CAL233182</v>
       </c>
       <c r="D238" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E238" s="1" t="str">
@@ -20482,8 +20497,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>615</v>
+      <c r="D239" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E239" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20501,8 +20517,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D240" s="2" t="s">
-        <v>615</v>
+      <c r="D240" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E240" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20520,8 +20537,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D241" s="2" t="s">
-        <v>615</v>
+      <c r="D241" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E241" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20539,8 +20557,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D242" s="2" t="s">
-        <v>615</v>
+      <c r="D242" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E242" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20558,8 +20577,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D243" s="2" t="s">
-        <v>615</v>
+      <c r="D243" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E243" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20577,8 +20597,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D244" s="2" t="s">
-        <v>615</v>
+      <c r="D244" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E244" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20596,8 +20617,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D245" s="2" t="s">
-        <v>615</v>
+      <c r="D245" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E245" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20615,8 +20637,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D246" s="2" t="s">
-        <v>615</v>
+      <c r="D246" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E246" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20634,8 +20657,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>615</v>
+      <c r="D247" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E247" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20653,8 +20677,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D248" s="2" t="s">
-        <v>615</v>
+      <c r="D248" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E248" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20672,8 +20697,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>615</v>
+      <c r="D249" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E249" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20691,8 +20717,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D250" s="2" t="s">
-        <v>615</v>
+      <c r="D250" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E250" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20710,8 +20737,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D251" s="2" t="s">
-        <v>615</v>
+      <c r="D251" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E251" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20729,7 +20757,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL227381</v>
       </c>
-      <c r="D252" s="22">
+      <c r="D252" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E252" s="1" t="str">
@@ -20748,8 +20777,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D253" s="2" t="s">
-        <v>615</v>
+      <c r="D253" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E253" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20767,7 +20797,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL233182</v>
       </c>
-      <c r="D254" s="22">
+      <c r="D254" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E254" s="1" t="str">
@@ -20786,7 +20817,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL220586</v>
       </c>
-      <c r="D255" s="22">
+      <c r="D255" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E255" s="1" t="str">
@@ -20805,8 +20837,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D256" s="2" t="s">
-        <v>615</v>
+      <c r="D256" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E256" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20824,7 +20857,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL227381</v>
       </c>
-      <c r="D257" s="22">
+      <c r="D257" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E257" s="1" t="str">
@@ -20843,8 +20877,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D258" s="2" t="s">
-        <v>615</v>
+      <c r="D258" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E258" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20862,7 +20897,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL227381</v>
       </c>
-      <c r="D259" s="22">
+      <c r="D259" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E259" s="1" t="str">
@@ -20881,8 +20917,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D260" s="2" t="s">
-        <v>615</v>
+      <c r="D260" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E260" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20900,8 +20937,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D261" s="2" t="s">
-        <v>615</v>
+      <c r="D261" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E261" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20919,7 +20957,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL220586</v>
       </c>
-      <c r="D262" s="22">
+      <c r="D262" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E262" s="1" t="str">
@@ -20938,7 +20977,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL233182</v>
       </c>
-      <c r="D263" s="22">
+      <c r="D263" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46751</v>
       </c>
       <c r="E263" s="1" t="str">
@@ -20957,8 +20997,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D264" s="2" t="s">
-        <v>615</v>
+      <c r="D264" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E264" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -20976,7 +21017,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL220586</v>
       </c>
-      <c r="D265" s="22">
+      <c r="D265" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46575</v>
       </c>
       <c r="E265" s="1" t="str">
@@ -20995,8 +21037,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D266" s="2" t="s">
-        <v>615</v>
+      <c r="D266" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E266" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21014,7 +21057,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL227381</v>
       </c>
-      <c r="D267" s="22">
+      <c r="D267" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E267" s="1" t="str">
@@ -21033,8 +21077,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D268" s="2" t="s">
-        <v>615</v>
+      <c r="D268" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E268" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21052,8 +21097,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D269" s="2" t="s">
-        <v>615</v>
+      <c r="D269" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E269" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21071,8 +21117,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D270" s="2" t="s">
-        <v>615</v>
+      <c r="D270" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E270" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21090,8 +21137,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D271" s="2" t="s">
-        <v>615</v>
+      <c r="D271" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E271" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21109,8 +21157,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D272" s="2" t="s">
-        <v>615</v>
+      <c r="D272" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E272" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21128,8 +21177,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D273" s="2" t="s">
-        <v>615</v>
+      <c r="D273" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E273" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21147,8 +21197,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D274" s="2" t="s">
-        <v>615</v>
+      <c r="D274" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E274" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21166,8 +21217,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D275" s="2" t="s">
-        <v>615</v>
+      <c r="D275" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E275" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21185,8 +21237,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D276" s="2" t="s">
-        <v>615</v>
+      <c r="D276" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E276" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21204,8 +21257,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D277" s="2" t="s">
-        <v>615</v>
+      <c r="D277" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E277" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21223,7 +21277,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL227381</v>
       </c>
-      <c r="D278" s="22">
+      <c r="D278" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E278" s="1" t="str">
@@ -21242,8 +21297,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D279" s="2" t="s">
-        <v>615</v>
+      <c r="D279" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E279" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21261,8 +21317,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D280" s="2" t="s">
-        <v>615</v>
+      <c r="D280" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E280" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21280,8 +21337,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D281" s="2" t="s">
-        <v>615</v>
+      <c r="D281" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E281" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21299,8 +21357,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D282" s="2" t="s">
-        <v>615</v>
+      <c r="D282" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E282" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21318,8 +21377,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D283" s="2" t="s">
-        <v>615</v>
+      <c r="D283" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E283" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21337,8 +21397,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D284" s="2" t="s">
-        <v>615</v>
+      <c r="D284" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E284" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21356,8 +21417,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D285" s="2" t="s">
-        <v>615</v>
+      <c r="D285" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E285" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21375,8 +21437,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D286" s="2" t="s">
-        <v>615</v>
+      <c r="D286" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E286" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21394,8 +21457,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D287" s="2" t="s">
-        <v>615</v>
+      <c r="D287" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E287" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21413,7 +21477,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL229703-6</v>
       </c>
-      <c r="D288" s="22">
+      <c r="D288" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46624</v>
       </c>
       <c r="E288" s="1" t="str">
@@ -21432,8 +21497,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D289" s="2" t="s">
-        <v>615</v>
+      <c r="D289" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E289" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21451,7 +21517,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL227381</v>
       </c>
-      <c r="D290" s="22">
+      <c r="D290" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E290" s="1" t="str">
@@ -21470,7 +21537,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL227381</v>
       </c>
-      <c r="D291" s="22">
+      <c r="D291" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46583</v>
       </c>
       <c r="E291" s="1" t="str">
@@ -21489,7 +21557,8 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>CAL231172</v>
       </c>
-      <c r="D292" s="22">
+      <c r="D292" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
         <v>46673</v>
       </c>
       <c r="E292" s="1" t="str">
@@ -21508,8 +21577,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D293" s="2" t="s">
-        <v>615</v>
+      <c r="D293" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E293" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21527,8 +21597,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D294" s="2" t="s">
-        <v>615</v>
+      <c r="D294" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E294" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21546,8 +21617,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D295" s="2" t="s">
-        <v>615</v>
+      <c r="D295" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E295" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21565,8 +21637,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D296" s="2" t="s">
-        <v>615</v>
+      <c r="D296" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E296" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21584,8 +21657,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D297" s="2" t="s">
-        <v>615</v>
+      <c r="D297" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E297" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21603,8 +21677,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D298" s="2" t="s">
-        <v>615</v>
+      <c r="D298" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E298" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21622,8 +21697,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D299" s="2" t="s">
-        <v>615</v>
+      <c r="D299" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E299" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21641,8 +21717,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>#N/A</v>
       </c>
-      <c r="D300" s="2" t="s">
-        <v>615</v>
+      <c r="D300" s="2" t="e">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>#N/A</v>
       </c>
       <c r="E300" s="1" t="e">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21660,8 +21737,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D301" s="2" t="s">
-        <v>615</v>
+      <c r="D301" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E301" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21679,8 +21757,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D302" s="2" t="s">
-        <v>615</v>
+      <c r="D302" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E302" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21698,8 +21777,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D303" s="2" t="s">
-        <v>615</v>
+      <c r="D303" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E303" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21717,8 +21797,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D304" s="2" t="s">
-        <v>615</v>
+      <c r="D304" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E304" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21736,8 +21817,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>#N/A</v>
       </c>
-      <c r="D305" s="2" t="s">
-        <v>615</v>
+      <c r="D305" s="2" t="e">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>#N/A</v>
       </c>
       <c r="E305" s="1" t="e">
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21755,8 +21837,9 @@
         <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EN:$EN)</f>
         <v>0</v>
       </c>
-      <c r="D306" s="2" t="s">
-        <v>615</v>
+      <c r="D306" s="2">
+        <f>_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EP:$EP)</f>
+        <v>0</v>
       </c>
       <c r="E306" s="1" t="str">
         <f ca="1">_xlfn.XLOOKUP(A:A,[1]Matriz!$E:$E,[1]Matriz!$EQ:$EQ)</f>
@@ -21791,7 +21874,7 @@
       <c r="B1" s="16" t="s">
         <v>613</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="16" t="s">
         <v>612</v>
       </c>
       <c r="D1" s="17" t="s">
@@ -27911,15 +27994,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6821B0B6-37CC-4636-93C0-247AA4FA530E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{58be8688-6625-4e52-80d8-c17f3a9ae08a}" enabled="0" method="" siteId="{58be8688-6625-4e52-80d8-c17f3a9ae08a}" removed="1"/>
